--- a/resources/templates/Template Laporan Pencapaian Standar Mutu FST.xlsx
+++ b/resources/templates/Template Laporan Pencapaian Standar Mutu FST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SiGKM\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AFF1EE-4A4C-481C-AB89-1A0665F08CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB9C6EC-17F9-4523-BC89-76F7E17EF5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>CAPAIAN STANDAR</t>
   </si>
@@ -89,13 +89,34 @@
   </si>
   <si>
     <t>STATUS</t>
+  </si>
+  <si>
+    <t>Mengetahui</t>
+  </si>
+  <si>
+    <t>Koordinator Prodi</t>
+  </si>
+  <si>
+    <t>Ketua GKM</t>
+  </si>
+  <si>
+    <t>Anggota GKM</t>
+  </si>
+  <si>
+    <t>(Dr. YULIANTO TRIWAHYUADI POLLY, S.Kom., M.Cs)</t>
+  </si>
+  <si>
+    <t>(CLARISSA ELFIRA AMOS PAH, M.T.I)</t>
+  </si>
+  <si>
+    <t>(NELCI DESSY RUMLAKLAK, S.KOM, M.KOM)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +193,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -343,7 +378,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -396,8 +431,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,9 +459,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -432,21 +479,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -521,7 +561,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
@@ -574,435 +614,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3932767</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>176953</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1397000</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>143086</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A711D237-A12C-42F4-AD2D-7BF76B01EB06}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6413500" y="155133886"/>
-          <a:ext cx="1790700" cy="1270000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Ketua GKM</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1336887</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>922866</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>113454</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="TextBox 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F208E89D-F804-4431-B4E5-7FEDB8720F2E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9812020" y="155134734"/>
-          <a:ext cx="1761913" cy="1239520"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Anggota GKM</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1394459</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1236133</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="TextBox 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F19A1ABD-7526-4EFB-BC51-1BA4117F7F6E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1775459" y="155166060"/>
-          <a:ext cx="1941407" cy="1270000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Mengetahui</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Koord. Prodi</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(…...........................)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1312,68 +923,68 @@
       <c r="A1" s="9"/>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="19"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="18"/>
       <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12"/>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="20"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="13"/>
     </row>
     <row r="3" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="21"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="22"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:11" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="22"/>
       <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="22"/>
       <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -1389,53 +1000,53 @@
     </row>
     <row r="8" spans="1:11" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:11" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="27" t="s">
+      <c r="D10" s="28"/>
+      <c r="E10" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
       <c r="E11" s="6" t="s">
         <v>4</v>
       </c>
@@ -1485,10 +1096,10 @@
       <c r="D16"/>
       <c r="E16"/>
       <c r="F16"/>
-      <c r="G16" t="s">
+      <c r="G16" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="H16"/>
+      <c r="H16" s="37"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1505,116 +1116,114 @@
       <c r="J17"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
+    <row r="18" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
+    <row r="19" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36" t="s">
+        <v>21</v>
+      </c>
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
+    <row r="20" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
+    <row r="21" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
       <c r="J21"/>
       <c r="K21"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
+    <row r="22" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
       <c r="J22"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
+    <row r="23" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
       <c r="J23"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
+    <row r="24" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="34"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
+    <row r="25" spans="2:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36" t="s">
+        <v>24</v>
+      </c>
       <c r="J25"/>
       <c r="K25"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:I10"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="D5:G5"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:I10"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="122" scale="72" orientation="landscape" r:id="rId1"/>
